--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fcorset/Documents/bureau/Papiers/encours/AnalyseSensibilite/degradation/Figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42DCF733-7EA8-F946-90AD-F971A7F1A5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775A0490-57E9-134C-924A-C3B7AC79D42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58440" yWindow="10320" windowWidth="28040" windowHeight="17440" xr2:uid="{37D0CA6D-01B9-8D49-BD9D-B7A2FC7232B6}"/>
+    <workbookView xWindow="46780" yWindow="4940" windowWidth="32720" windowHeight="20420" xr2:uid="{37D0CA6D-01B9-8D49-BD9D-B7A2FC7232B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>tau</t>
   </si>
@@ -69,20 +69,27 @@
     <t>observations</t>
   </si>
   <si>
-    <t>Not good</t>
+    <t>M</t>
   </si>
   <si>
-    <t>0.1</t>
+    <t>L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -108,8 +115,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,13 +432,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BAD8E64-6442-2E45-B5B2-353746D206C5}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="11" max="11" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -447,27 +455,33 @@
         <v>7</v>
       </c>
       <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -482,24 +496,24 @@
         <v>0.2</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>1.4</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>8.4499999999999993</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -514,24 +528,24 @@
         <v>0.2</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>1.56</v>
+        <v>10</v>
       </c>
       <c r="J3">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -546,33 +560,30 @@
         <v>0.2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>15.96</v>
-      </c>
-      <c r="K4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -581,33 +592,30 @@
         <v>0.2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>50</v>
-      </c>
-      <c r="I5" t="s">
-        <v>12</v>
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>16.53</v>
-      </c>
-      <c r="K5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>1.2</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -616,30 +624,30 @@
         <v>0.2</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>15.73</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -648,25 +656,22 @@
         <v>0.2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G7">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>10</v>
-      </c>
-      <c r="K7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -674,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -683,30 +688,30 @@
         <v>0.2</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G8">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>14.58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -715,30 +720,30 @@
         <v>0.2</v>
       </c>
       <c r="F9">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G9">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>1.39</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>14.37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B10">
         <v>1</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -747,22 +752,22 @@
         <v>0.2</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>1.36</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>14.48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -779,27 +784,27 @@
         <v>0.2</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G11">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>1.58</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -811,33 +816,30 @@
         <v>0.2</v>
       </c>
       <c r="F12">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G12">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>31.91</v>
-      </c>
-      <c r="K12" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <v>0.5</v>
       </c>
       <c r="C13">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -846,30 +848,30 @@
         <v>0.2</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G13">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H13">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>1.49</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -878,24 +880,30 @@
         <v>0.2</v>
       </c>
       <c r="F14">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G14">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B15">
         <v>2</v>
       </c>
       <c r="C15">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -904,21 +912,27 @@
         <v>0.2</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -930,16 +944,22 @@
         <v>0.2</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="G16">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
@@ -953,67 +973,1141 @@
         <v>1</v>
       </c>
       <c r="E17">
+        <v>0.5</v>
+      </c>
+      <c r="F17">
+        <v>80</v>
+      </c>
+      <c r="G17">
+        <v>100</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0.5</v>
+      </c>
+      <c r="F18">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>100</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>10</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>0.5</v>
+      </c>
+      <c r="F19">
+        <v>80</v>
+      </c>
+      <c r="G19">
+        <v>100</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>0.75</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>0.5</v>
+      </c>
+      <c r="F20">
+        <v>80</v>
+      </c>
+      <c r="G20">
+        <v>100</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>0.75</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>0.5</v>
+      </c>
+      <c r="F21">
+        <v>80</v>
+      </c>
+      <c r="G21">
+        <v>100</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>10</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>0.75</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>0.5</v>
+      </c>
+      <c r="F22">
+        <v>80</v>
+      </c>
+      <c r="G22">
+        <v>100</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>1</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1.2</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>0.5</v>
+      </c>
+      <c r="F23">
+        <v>80</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>1.2</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>0.5</v>
+      </c>
+      <c r="F24">
+        <v>80</v>
+      </c>
+      <c r="G24">
+        <v>100</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>10</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25">
+        <v>1.2</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0.5</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25">
+        <v>100</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>1</v>
+      </c>
+      <c r="B26">
+        <v>0.5</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>0.5</v>
+      </c>
+      <c r="F26">
+        <v>80</v>
+      </c>
+      <c r="G26">
+        <v>100</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>5</v>
+      </c>
+      <c r="B27">
+        <v>0.5</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>0.5</v>
+      </c>
+      <c r="F27">
+        <v>80</v>
+      </c>
+      <c r="G27">
+        <v>100</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>10</v>
+      </c>
+      <c r="B28">
+        <v>0.5</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>0.5</v>
+      </c>
+      <c r="F28">
+        <v>80</v>
+      </c>
+      <c r="G28">
+        <v>100</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>10</v>
+      </c>
+      <c r="J28">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>1</v>
+      </c>
+      <c r="B29">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0.5</v>
+      </c>
+      <c r="F29">
+        <v>80</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>10</v>
+      </c>
+      <c r="J29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>5</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>0.5</v>
+      </c>
+      <c r="F30">
+        <v>80</v>
+      </c>
+      <c r="G30">
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>10</v>
+      </c>
+      <c r="J30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>10</v>
+      </c>
+      <c r="B31">
+        <v>2</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>0.5</v>
+      </c>
+      <c r="F31">
+        <v>80</v>
+      </c>
+      <c r="G31">
+        <v>100</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+      <c r="I31">
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F32" s="1">
+        <v>80</v>
+      </c>
+      <c r="G32" s="1">
+        <v>100</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
+      <c r="I32" s="1">
+        <v>10</v>
+      </c>
+      <c r="J32" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>1</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F33" s="1">
+        <v>80</v>
+      </c>
+      <c r="G33" s="1">
+        <v>100</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33" s="1">
+        <v>10</v>
+      </c>
+      <c r="J33" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>10</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1</v>
+      </c>
+      <c r="D34" s="1">
+        <v>1</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F34" s="1">
+        <v>80</v>
+      </c>
+      <c r="G34" s="1">
+        <v>100</v>
+      </c>
+      <c r="H34" s="1">
+        <v>1</v>
+      </c>
+      <c r="I34" s="1">
+        <v>10</v>
+      </c>
+      <c r="J34" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>1</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D35" s="1">
+        <v>1</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F35" s="1">
+        <v>80</v>
+      </c>
+      <c r="G35" s="1">
+        <v>100</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>10</v>
+      </c>
+      <c r="J35" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>5</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D36" s="1">
+        <v>1</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F36" s="1">
+        <v>80</v>
+      </c>
+      <c r="G36" s="1">
+        <v>100</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>10</v>
+      </c>
+      <c r="J36" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>10</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F37" s="1">
+        <v>80</v>
+      </c>
+      <c r="G37" s="1">
+        <v>100</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
+        <v>10</v>
+      </c>
+      <c r="J37" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>1</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F38" s="1">
+        <v>80</v>
+      </c>
+      <c r="G38" s="1">
+        <v>100</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>10</v>
+      </c>
+      <c r="J38" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>5</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F39" s="1">
+        <v>80</v>
+      </c>
+      <c r="G39" s="1">
+        <v>100</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
+        <v>10</v>
+      </c>
+      <c r="J39" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>10</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1.2</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F40" s="1">
+        <v>80</v>
+      </c>
+      <c r="G40" s="1">
+        <v>100</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
+        <v>10</v>
+      </c>
+      <c r="J40" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>1</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F41" s="1">
+        <v>80</v>
+      </c>
+      <c r="G41" s="1">
+        <v>100</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
+        <v>10</v>
+      </c>
+      <c r="J41" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>5</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F42" s="1">
+        <v>80</v>
+      </c>
+      <c r="G42" s="1">
+        <v>100</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
+        <v>10</v>
+      </c>
+      <c r="J42" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>10</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F43" s="1">
+        <v>80</v>
+      </c>
+      <c r="G43" s="1">
+        <v>100</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1">
+        <v>10</v>
+      </c>
+      <c r="J43" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>1</v>
+      </c>
+      <c r="B44" s="1">
+        <v>2</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F44" s="1">
+        <v>80</v>
+      </c>
+      <c r="G44" s="1">
+        <v>100</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>10</v>
+      </c>
+      <c r="J44" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>5</v>
+      </c>
+      <c r="B45" s="1">
+        <v>2</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F45" s="1">
+        <v>80</v>
+      </c>
+      <c r="G45" s="1">
+        <v>100</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
+        <v>10</v>
+      </c>
+      <c r="J45" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>10</v>
+      </c>
+      <c r="B46" s="1">
+        <v>2</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="F46" s="1">
+        <v>80</v>
+      </c>
+      <c r="G46" s="1">
+        <v>100</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
+        <v>10</v>
+      </c>
+      <c r="J46" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>1</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
         <v>0.2</v>
       </c>
-      <c r="F17">
+      <c r="F47">
+        <v>80</v>
+      </c>
+      <c r="G47">
+        <v>100</v>
+      </c>
+      <c r="H47">
+        <v>1</v>
+      </c>
+      <c r="I47">
+        <v>10</v>
+      </c>
+      <c r="J47">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>1</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0.2</v>
+      </c>
+      <c r="F48">
+        <v>80</v>
+      </c>
+      <c r="G48">
+        <v>100</v>
+      </c>
+      <c r="H48">
+        <v>1</v>
+      </c>
+      <c r="I48">
+        <v>10</v>
+      </c>
+      <c r="J48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>1</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>0.2</v>
+      </c>
+      <c r="F49">
+        <v>80</v>
+      </c>
+      <c r="G49">
+        <v>100</v>
+      </c>
+      <c r="H49">
+        <v>1</v>
+      </c>
+      <c r="I49">
+        <v>10</v>
+      </c>
+      <c r="J49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>1</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>0.2</v>
+      </c>
+      <c r="F50">
+        <v>80</v>
+      </c>
+      <c r="G50">
+        <v>100</v>
+      </c>
+      <c r="H50">
         <v>5</v>
       </c>
-      <c r="G17">
-        <v>10</v>
-      </c>
-      <c r="H17">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>1</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
+      <c r="I50">
+        <v>10</v>
+      </c>
+      <c r="J50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
         <v>0.2</v>
       </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>50</v>
-      </c>
-      <c r="H18">
+      <c r="F51">
+        <v>80</v>
+      </c>
+      <c r="G51">
+        <v>100</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>50</v>
+      </c>
+      <c r="J51">
         <v>500</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52">
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
         <v>0.2</v>
       </c>
-      <c r="F19">
+      <c r="F52">
+        <v>80</v>
+      </c>
+      <c r="G52">
+        <v>100</v>
+      </c>
+      <c r="H52">
         <v>5</v>
       </c>
-      <c r="G19">
-        <v>10</v>
-      </c>
-      <c r="H19">
+      <c r="I52">
+        <v>10</v>
+      </c>
+      <c r="J52">
         <v>500</v>
       </c>
     </row>

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fcorset/Documents/bureau/Papiers/encours/AnalyseSensibilite/degradation/Figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775A0490-57E9-134C-924A-C3B7AC79D42B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1030BC2A-3BF9-704B-8775-24CE2E75F0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46780" yWindow="4940" windowWidth="32720" windowHeight="20420" xr2:uid="{37D0CA6D-01B9-8D49-BD9D-B7A2FC7232B6}"/>
+    <workbookView xWindow="47860" yWindow="2420" windowWidth="32720" windowHeight="20420" xr2:uid="{37D0CA6D-01B9-8D49-BD9D-B7A2FC7232B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -496,10 +496,10 @@
         <v>0.2</v>
       </c>
       <c r="F2">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -528,10 +528,10 @@
         <v>0.2</v>
       </c>
       <c r="F3">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -560,10 +560,10 @@
         <v>0.2</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -592,10 +592,10 @@
         <v>0.2</v>
       </c>
       <c r="F5">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -624,10 +624,10 @@
         <v>0.2</v>
       </c>
       <c r="F6">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -656,10 +656,10 @@
         <v>0.2</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G7">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -688,10 +688,10 @@
         <v>0.2</v>
       </c>
       <c r="F8">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -720,10 +720,10 @@
         <v>0.2</v>
       </c>
       <c r="F9">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G9">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -752,10 +752,10 @@
         <v>0.2</v>
       </c>
       <c r="F10">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -784,10 +784,10 @@
         <v>0.2</v>
       </c>
       <c r="F11">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G11">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -816,10 +816,10 @@
         <v>0.2</v>
       </c>
       <c r="F12">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -848,10 +848,10 @@
         <v>0.2</v>
       </c>
       <c r="F13">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G13">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -880,10 +880,10 @@
         <v>0.2</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -912,10 +912,10 @@
         <v>0.2</v>
       </c>
       <c r="F15">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -944,10 +944,10 @@
         <v>0.2</v>
       </c>
       <c r="F16">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G16">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -976,10 +976,10 @@
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G17">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1008,10 +1008,10 @@
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1040,10 +1040,10 @@
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G19">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -1072,10 +1072,10 @@
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -1104,10 +1104,10 @@
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G21">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -1136,10 +1136,10 @@
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G22">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -1168,10 +1168,10 @@
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G23">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -1200,10 +1200,10 @@
         <v>0.5</v>
       </c>
       <c r="F24">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1232,10 +1232,10 @@
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G25">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.5</v>
       </c>
       <c r="F26">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1296,10 +1296,10 @@
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G27">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1328,10 +1328,10 @@
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G28">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1360,10 +1360,10 @@
         <v>0.5</v>
       </c>
       <c r="F29">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G29">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1392,10 +1392,10 @@
         <v>0.5</v>
       </c>
       <c r="F30">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G30">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1424,10 +1424,10 @@
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G31">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1455,11 +1455,11 @@
       <c r="E32" s="1">
         <v>0.8</v>
       </c>
-      <c r="F32" s="1">
-        <v>80</v>
-      </c>
-      <c r="G32" s="1">
-        <v>100</v>
+      <c r="F32">
+        <v>40</v>
+      </c>
+      <c r="G32">
+        <v>50</v>
       </c>
       <c r="H32" s="1">
         <v>1</v>
@@ -1487,11 +1487,11 @@
       <c r="E33" s="1">
         <v>0.8</v>
       </c>
-      <c r="F33" s="1">
-        <v>80</v>
-      </c>
-      <c r="G33" s="1">
-        <v>100</v>
+      <c r="F33">
+        <v>40</v>
+      </c>
+      <c r="G33">
+        <v>50</v>
       </c>
       <c r="H33" s="1">
         <v>1</v>
@@ -1519,11 +1519,11 @@
       <c r="E34" s="1">
         <v>0.8</v>
       </c>
-      <c r="F34" s="1">
-        <v>80</v>
-      </c>
-      <c r="G34" s="1">
-        <v>100</v>
+      <c r="F34">
+        <v>40</v>
+      </c>
+      <c r="G34">
+        <v>50</v>
       </c>
       <c r="H34" s="1">
         <v>1</v>
@@ -1551,11 +1551,11 @@
       <c r="E35" s="1">
         <v>0.8</v>
       </c>
-      <c r="F35" s="1">
-        <v>80</v>
-      </c>
-      <c r="G35" s="1">
-        <v>100</v>
+      <c r="F35">
+        <v>40</v>
+      </c>
+      <c r="G35">
+        <v>50</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
@@ -1583,11 +1583,11 @@
       <c r="E36" s="1">
         <v>0.8</v>
       </c>
-      <c r="F36" s="1">
-        <v>80</v>
-      </c>
-      <c r="G36" s="1">
-        <v>100</v>
+      <c r="F36">
+        <v>40</v>
+      </c>
+      <c r="G36">
+        <v>50</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
@@ -1615,11 +1615,11 @@
       <c r="E37" s="1">
         <v>0.8</v>
       </c>
-      <c r="F37" s="1">
-        <v>80</v>
-      </c>
-      <c r="G37" s="1">
-        <v>100</v>
+      <c r="F37">
+        <v>40</v>
+      </c>
+      <c r="G37">
+        <v>50</v>
       </c>
       <c r="H37" s="1">
         <v>1</v>
@@ -1647,11 +1647,11 @@
       <c r="E38" s="1">
         <v>0.8</v>
       </c>
-      <c r="F38" s="1">
-        <v>80</v>
-      </c>
-      <c r="G38" s="1">
-        <v>100</v>
+      <c r="F38">
+        <v>40</v>
+      </c>
+      <c r="G38">
+        <v>50</v>
       </c>
       <c r="H38" s="1">
         <v>1</v>
@@ -1679,11 +1679,11 @@
       <c r="E39" s="1">
         <v>0.8</v>
       </c>
-      <c r="F39" s="1">
-        <v>80</v>
-      </c>
-      <c r="G39" s="1">
-        <v>100</v>
+      <c r="F39">
+        <v>40</v>
+      </c>
+      <c r="G39">
+        <v>50</v>
       </c>
       <c r="H39" s="1">
         <v>1</v>
@@ -1711,11 +1711,11 @@
       <c r="E40" s="1">
         <v>0.8</v>
       </c>
-      <c r="F40" s="1">
-        <v>80</v>
-      </c>
-      <c r="G40" s="1">
-        <v>100</v>
+      <c r="F40">
+        <v>40</v>
+      </c>
+      <c r="G40">
+        <v>50</v>
       </c>
       <c r="H40" s="1">
         <v>1</v>
@@ -1743,11 +1743,11 @@
       <c r="E41" s="1">
         <v>0.8</v>
       </c>
-      <c r="F41" s="1">
-        <v>80</v>
-      </c>
-      <c r="G41" s="1">
-        <v>100</v>
+      <c r="F41">
+        <v>40</v>
+      </c>
+      <c r="G41">
+        <v>50</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
@@ -1775,11 +1775,11 @@
       <c r="E42" s="1">
         <v>0.8</v>
       </c>
-      <c r="F42" s="1">
-        <v>80</v>
-      </c>
-      <c r="G42" s="1">
-        <v>100</v>
+      <c r="F42">
+        <v>40</v>
+      </c>
+      <c r="G42">
+        <v>50</v>
       </c>
       <c r="H42" s="1">
         <v>1</v>
@@ -1807,11 +1807,11 @@
       <c r="E43" s="1">
         <v>0.8</v>
       </c>
-      <c r="F43" s="1">
-        <v>80</v>
-      </c>
-      <c r="G43" s="1">
-        <v>100</v>
+      <c r="F43">
+        <v>40</v>
+      </c>
+      <c r="G43">
+        <v>50</v>
       </c>
       <c r="H43" s="1">
         <v>1</v>
@@ -1839,11 +1839,11 @@
       <c r="E44" s="1">
         <v>0.8</v>
       </c>
-      <c r="F44" s="1">
-        <v>80</v>
-      </c>
-      <c r="G44" s="1">
-        <v>100</v>
+      <c r="F44">
+        <v>40</v>
+      </c>
+      <c r="G44">
+        <v>50</v>
       </c>
       <c r="H44" s="1">
         <v>1</v>
@@ -1871,11 +1871,11 @@
       <c r="E45" s="1">
         <v>0.8</v>
       </c>
-      <c r="F45" s="1">
-        <v>80</v>
-      </c>
-      <c r="G45" s="1">
-        <v>100</v>
+      <c r="F45">
+        <v>40</v>
+      </c>
+      <c r="G45">
+        <v>50</v>
       </c>
       <c r="H45" s="1">
         <v>1</v>
@@ -1903,11 +1903,11 @@
       <c r="E46" s="1">
         <v>0.8</v>
       </c>
-      <c r="F46" s="1">
-        <v>80</v>
-      </c>
-      <c r="G46" s="1">
-        <v>100</v>
+      <c r="F46">
+        <v>40</v>
+      </c>
+      <c r="G46">
+        <v>50</v>
       </c>
       <c r="H46" s="1">
         <v>1</v>
@@ -1936,10 +1936,10 @@
         <v>0.2</v>
       </c>
       <c r="F47">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G47">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -1968,10 +1968,10 @@
         <v>0.2</v>
       </c>
       <c r="F48">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2000,10 +2000,10 @@
         <v>0.2</v>
       </c>
       <c r="F49">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G49">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2032,10 +2032,10 @@
         <v>0.2</v>
       </c>
       <c r="F50">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G50">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H50">
         <v>5</v>
@@ -2064,10 +2064,10 @@
         <v>0.2</v>
       </c>
       <c r="F51">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G51">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -2096,10 +2096,10 @@
         <v>0.2</v>
       </c>
       <c r="F52">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G52">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H52">
         <v>5</v>

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fcorset/Documents/bureau/Papiers/encours/AnalyseSensibilite/degradation/Figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1030BC2A-3BF9-704B-8775-24CE2E75F0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC4F51B-73B4-5B4F-9BCA-1B7AB7FB7CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47860" yWindow="2420" windowWidth="32720" windowHeight="20420" xr2:uid="{37D0CA6D-01B9-8D49-BD9D-B7A2FC7232B6}"/>
+    <workbookView xWindow="1720" yWindow="1040" windowWidth="32720" windowHeight="20420" xr2:uid="{37D0CA6D-01B9-8D49-BD9D-B7A2FC7232B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>tau</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>Not good</t>
   </si>
 </sst>
 </file>
@@ -510,6 +513,15 @@
       <c r="J2">
         <v>50</v>
       </c>
+      <c r="K2">
+        <v>45</v>
+      </c>
+      <c r="L2">
+        <v>4.21</v>
+      </c>
+      <c r="M2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
@@ -541,6 +553,12 @@
       </c>
       <c r="J3">
         <v>50</v>
+      </c>
+      <c r="K3">
+        <v>28.04</v>
+      </c>
+      <c r="L3">
+        <v>2.14</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -1,98 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10912"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fcorset/Documents/bureau/Papiers/encours/AnalyseSensibilite/degradation/Figures/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC4F51B-73B4-5B4F-9BCA-1B7AB7FB7CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="1040" windowWidth="32720" windowHeight="20420" xr2:uid="{37D0CA6D-01B9-8D49-BD9D-B7A2FC7232B6}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>tau</t>
-  </si>
-  <si>
-    <t>alpha</t>
-  </si>
-  <si>
-    <t>beta</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>C_I</t>
-  </si>
-  <si>
-    <t>C_P</t>
-  </si>
-  <si>
-    <t>C_C</t>
-  </si>
-  <si>
-    <t>rho</t>
-  </si>
-  <si>
-    <t>L_opt</t>
-  </si>
-  <si>
-    <t>Cout_opt</t>
-  </si>
-  <si>
-    <t>observations</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Not good</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -120,26 +54,20 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -149,44 +77,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -213,32 +141,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -265,24 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -294,195 +186,242 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BAD8E64-6442-2E45-B5B2-353746D206C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tau</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>rho</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>C_I</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>C_P</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>C_C</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>L_opt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cout_opt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>observations</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -514,16 +453,18 @@
         <v>50</v>
       </c>
       <c r="K2">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>4.21</v>
-      </c>
-      <c r="M2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Not good</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3">
         <v>5</v>
       </c>
@@ -561,7 +502,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4">
       <c r="A4">
         <v>10</v>
       </c>
@@ -593,7 +534,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5">
       <c r="A5">
         <v>1</v>
       </c>
@@ -625,7 +566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -657,7 +598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7">
       <c r="A7">
         <v>10</v>
       </c>
@@ -689,7 +630,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8">
       <c r="A8">
         <v>1</v>
       </c>
@@ -721,7 +662,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9">
       <c r="A9">
         <v>5</v>
       </c>
@@ -753,7 +694,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10">
       <c r="A10">
         <v>10</v>
       </c>
@@ -785,7 +726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="11">
       <c r="A11">
         <v>1</v>
       </c>
@@ -817,7 +758,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="12">
       <c r="A12">
         <v>5</v>
       </c>
@@ -849,7 +790,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="13">
       <c r="A13">
         <v>10</v>
       </c>
@@ -881,7 +822,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="14">
       <c r="A14">
         <v>1</v>
       </c>
@@ -913,7 +854,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="15">
       <c r="A15">
         <v>5</v>
       </c>
@@ -945,7 +886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16">
       <c r="A16">
         <v>10</v>
       </c>
@@ -977,7 +918,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17">
       <c r="A17">
         <v>1</v>
       </c>
@@ -1009,7 +950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18">
       <c r="A18">
         <v>5</v>
       </c>
@@ -1041,7 +982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19">
       <c r="A19">
         <v>10</v>
       </c>
@@ -1073,7 +1014,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20">
       <c r="A20">
         <v>1</v>
       </c>
@@ -1105,7 +1046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21">
       <c r="A21">
         <v>5</v>
       </c>
@@ -1137,7 +1078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22">
       <c r="A22">
         <v>10</v>
       </c>
@@ -1169,7 +1110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23">
       <c r="A23">
         <v>1</v>
       </c>
@@ -1201,7 +1142,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24">
       <c r="A24">
         <v>5</v>
       </c>
@@ -1233,7 +1174,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25">
       <c r="A25">
         <v>10</v>
       </c>
@@ -1265,7 +1206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26">
       <c r="A26">
         <v>1</v>
       </c>
@@ -1297,7 +1238,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27">
       <c r="A27">
         <v>5</v>
       </c>
@@ -1329,7 +1270,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28">
       <c r="A28">
         <v>10</v>
       </c>
@@ -1361,7 +1302,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29">
       <c r="A29">
         <v>1</v>
       </c>
@@ -1393,7 +1334,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30">
       <c r="A30">
         <v>5</v>
       </c>
@@ -1425,7 +1366,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31">
       <c r="A31">
         <v>10</v>
       </c>
@@ -1457,20 +1398,20 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
-        <v>1</v>
-      </c>
-      <c r="B32" s="1">
-        <v>1</v>
-      </c>
-      <c r="C32" s="1">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
+    <row r="32">
+      <c r="A32">
+        <v>1</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
         <v>0.8</v>
       </c>
       <c r="F32">
@@ -1479,30 +1420,30 @@
       <c r="G32">
         <v>50</v>
       </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
-        <v>10</v>
-      </c>
-      <c r="J32" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+      <c r="J32">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
         <v>5</v>
       </c>
-      <c r="B33" s="1">
-        <v>1</v>
-      </c>
-      <c r="C33" s="1">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="B33">
+        <v>1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
         <v>0.8</v>
       </c>
       <c r="F33">
@@ -1511,30 +1452,30 @@
       <c r="G33">
         <v>50</v>
       </c>
-      <c r="H33" s="1">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1">
-        <v>10</v>
-      </c>
-      <c r="J33" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A34" s="1">
-        <v>10</v>
-      </c>
-      <c r="B34" s="1">
-        <v>1</v>
-      </c>
-      <c r="C34" s="1">
-        <v>1</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
+      <c r="H33">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>10</v>
+      </c>
+      <c r="J33">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>10</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
         <v>0.8</v>
       </c>
       <c r="F34">
@@ -1543,30 +1484,30 @@
       <c r="G34">
         <v>50</v>
       </c>
-      <c r="H34" s="1">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
-        <v>10</v>
-      </c>
-      <c r="J34" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
-        <v>1</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1">
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>10</v>
+      </c>
+      <c r="J34">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
         <v>0.75</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
         <v>0.8</v>
       </c>
       <c r="F35">
@@ -1575,30 +1516,30 @@
       <c r="G35">
         <v>50</v>
       </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>10</v>
-      </c>
-      <c r="J35" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>10</v>
+      </c>
+      <c r="J35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
         <v>5</v>
       </c>
-      <c r="B36" s="1">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1">
+      <c r="B36">
+        <v>1</v>
+      </c>
+      <c r="C36">
         <v>0.75</v>
       </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
         <v>0.8</v>
       </c>
       <c r="F36">
@@ -1607,30 +1548,30 @@
       <c r="G36">
         <v>50</v>
       </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>10</v>
-      </c>
-      <c r="J36" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
-        <v>10</v>
-      </c>
-      <c r="B37" s="1">
-        <v>1</v>
-      </c>
-      <c r="C37" s="1">
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>10</v>
+      </c>
+      <c r="B37">
+        <v>1</v>
+      </c>
+      <c r="C37">
         <v>0.75</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
         <v>0.8</v>
       </c>
       <c r="F37">
@@ -1639,30 +1580,30 @@
       <c r="G37">
         <v>50</v>
       </c>
-      <c r="H37" s="1">
-        <v>1</v>
-      </c>
-      <c r="I37" s="1">
-        <v>10</v>
-      </c>
-      <c r="J37" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
-        <v>1</v>
-      </c>
-      <c r="B38" s="1">
-        <v>1</v>
-      </c>
-      <c r="C38" s="1">
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>10</v>
+      </c>
+      <c r="J37">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
         <v>1.2</v>
       </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
         <v>0.8</v>
       </c>
       <c r="F38">
@@ -1671,30 +1612,30 @@
       <c r="G38">
         <v>50</v>
       </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
-        <v>10</v>
-      </c>
-      <c r="J38" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>10</v>
+      </c>
+      <c r="J38">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
         <v>5</v>
       </c>
-      <c r="B39" s="1">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1">
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
         <v>1.2</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
         <v>0.8</v>
       </c>
       <c r="F39">
@@ -1703,30 +1644,30 @@
       <c r="G39">
         <v>50</v>
       </c>
-      <c r="H39" s="1">
-        <v>1</v>
-      </c>
-      <c r="I39" s="1">
-        <v>10</v>
-      </c>
-      <c r="J39" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
-        <v>10</v>
-      </c>
-      <c r="B40" s="1">
-        <v>1</v>
-      </c>
-      <c r="C40" s="1">
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>10</v>
+      </c>
+      <c r="J39">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40">
+        <v>1</v>
+      </c>
+      <c r="C40">
         <v>1.2</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
+      <c r="D40">
+        <v>1</v>
+      </c>
+      <c r="E40">
         <v>0.8</v>
       </c>
       <c r="F40">
@@ -1735,30 +1676,30 @@
       <c r="G40">
         <v>50</v>
       </c>
-      <c r="H40" s="1">
-        <v>1</v>
-      </c>
-      <c r="I40" s="1">
-        <v>10</v>
-      </c>
-      <c r="J40" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A41" s="1">
-        <v>1</v>
-      </c>
-      <c r="B41" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>10</v>
+      </c>
+      <c r="J40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1</v>
+      </c>
+      <c r="B41">
+        <v>0.5</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>1</v>
+      </c>
+      <c r="E41">
         <v>0.8</v>
       </c>
       <c r="F41">
@@ -1767,30 +1708,30 @@
       <c r="G41">
         <v>50</v>
       </c>
-      <c r="H41" s="1">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1">
-        <v>10</v>
-      </c>
-      <c r="J41" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A42" s="1">
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41">
+        <v>10</v>
+      </c>
+      <c r="J41">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
         <v>5</v>
       </c>
-      <c r="B42" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="C42" s="1">
-        <v>1</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
+      <c r="B42">
+        <v>0.5</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
         <v>0.8</v>
       </c>
       <c r="F42">
@@ -1799,30 +1740,30 @@
       <c r="G42">
         <v>50</v>
       </c>
-      <c r="H42" s="1">
-        <v>1</v>
-      </c>
-      <c r="I42" s="1">
-        <v>10</v>
-      </c>
-      <c r="J42" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A43" s="1">
-        <v>10</v>
-      </c>
-      <c r="B43" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="C43" s="1">
-        <v>1</v>
-      </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1">
+      <c r="H42">
+        <v>1</v>
+      </c>
+      <c r="I42">
+        <v>10</v>
+      </c>
+      <c r="J42">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>10</v>
+      </c>
+      <c r="B43">
+        <v>0.5</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
         <v>0.8</v>
       </c>
       <c r="F43">
@@ -1831,30 +1772,30 @@
       <c r="G43">
         <v>50</v>
       </c>
-      <c r="H43" s="1">
-        <v>1</v>
-      </c>
-      <c r="I43" s="1">
-        <v>10</v>
-      </c>
-      <c r="J43" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A44" s="1">
-        <v>1</v>
-      </c>
-      <c r="B44" s="1">
+      <c r="H43">
+        <v>1</v>
+      </c>
+      <c r="I43">
+        <v>10</v>
+      </c>
+      <c r="J43">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44">
         <v>2</v>
       </c>
-      <c r="C44" s="1">
-        <v>1</v>
-      </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="1">
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
         <v>0.8</v>
       </c>
       <c r="F44">
@@ -1863,30 +1804,30 @@
       <c r="G44">
         <v>50</v>
       </c>
-      <c r="H44" s="1">
-        <v>1</v>
-      </c>
-      <c r="I44" s="1">
-        <v>10</v>
-      </c>
-      <c r="J44" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A45" s="1">
+      <c r="H44">
+        <v>1</v>
+      </c>
+      <c r="I44">
+        <v>10</v>
+      </c>
+      <c r="J44">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
         <v>5</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45">
         <v>2</v>
       </c>
-      <c r="C45" s="1">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="1">
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
         <v>0.8</v>
       </c>
       <c r="F45">
@@ -1895,30 +1836,30 @@
       <c r="G45">
         <v>50</v>
       </c>
-      <c r="H45" s="1">
-        <v>1</v>
-      </c>
-      <c r="I45" s="1">
-        <v>10</v>
-      </c>
-      <c r="J45" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A46" s="1">
-        <v>10</v>
-      </c>
-      <c r="B46" s="1">
+      <c r="H45">
+        <v>1</v>
+      </c>
+      <c r="I45">
+        <v>10</v>
+      </c>
+      <c r="J45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>10</v>
+      </c>
+      <c r="B46">
         <v>2</v>
       </c>
-      <c r="C46" s="1">
-        <v>1</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
         <v>0.8</v>
       </c>
       <c r="F46">
@@ -1927,17 +1868,17 @@
       <c r="G46">
         <v>50</v>
       </c>
-      <c r="H46" s="1">
-        <v>1</v>
-      </c>
-      <c r="I46" s="1">
-        <v>10</v>
-      </c>
-      <c r="J46" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="H46">
+        <v>1</v>
+      </c>
+      <c r="I46">
+        <v>10</v>
+      </c>
+      <c r="J46">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47">
         <v>1</v>
       </c>
@@ -1969,7 +1910,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48">
       <c r="A48">
         <v>1</v>
       </c>
@@ -2001,7 +1942,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49">
       <c r="A49">
         <v>1</v>
       </c>
@@ -2033,7 +1974,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50">
       <c r="A50">
         <v>1</v>
       </c>
@@ -2065,7 +2006,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51">
       <c r="A51">
         <v>1</v>
       </c>
@@ -2097,7 +2038,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52">
       <c r="A52">
         <v>1</v>
       </c>

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -533,6 +533,12 @@
       <c r="J4">
         <v>50</v>
       </c>
+      <c r="K4">
+        <v>45</v>
+      </c>
+      <c r="L4">
+        <v>2.220207255333746</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5">
@@ -597,6 +603,12 @@
       <c r="J6">
         <v>50</v>
       </c>
+      <c r="K6">
+        <v>45</v>
+      </c>
+      <c r="L6">
+        <v>1.302762010414465</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -693,6 +705,12 @@
       <c r="J9">
         <v>50</v>
       </c>
+      <c r="K9">
+        <v>7.42</v>
+      </c>
+      <c r="L9">
+        <v>2.668747922270521</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10">
@@ -756,6 +774,12 @@
       </c>
       <c r="J11">
         <v>50</v>
+      </c>
+      <c r="K11">
+        <v>44.34</v>
+      </c>
+      <c r="L11">
+        <v>0.4664116079964298</v>
       </c>
     </row>
     <row r="12">
@@ -821,6 +845,12 @@
       <c r="J13">
         <v>50</v>
       </c>
+      <c r="K13">
+        <v>27.98</v>
+      </c>
+      <c r="L13">
+        <v>1.057000782690142</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14">
@@ -2068,6 +2098,12 @@
       </c>
       <c r="J52">
         <v>500</v>
+      </c>
+      <c r="K52">
+        <v>37.87</v>
+      </c>
+      <c r="L52">
+        <v>9.946531140520923</v>
       </c>
     </row>
   </sheetData>

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -453,10 +453,10 @@
         <v>50</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>4.545732961314433</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -496,10 +496,10 @@
         <v>50</v>
       </c>
       <c r="K3">
-        <v>28.04</v>
+        <v>27.98</v>
       </c>
       <c r="L3">
-        <v>2.14</v>
+        <v>2.114001565380284</v>
       </c>
     </row>
     <row r="4">
@@ -570,6 +570,12 @@
       </c>
       <c r="J5">
         <v>50</v>
+      </c>
+      <c r="K5">
+        <v>45</v>
+      </c>
+      <c r="L5">
+        <v>4.545732961314433</v>
       </c>
     </row>
     <row r="6">
@@ -604,10 +610,10 @@
         <v>50</v>
       </c>
       <c r="K6">
-        <v>45</v>
+        <v>43.34</v>
       </c>
       <c r="L6">
-        <v>1.302762010414465</v>
+        <v>1.408069095309405</v>
       </c>
     </row>
     <row r="7">
@@ -641,6 +647,12 @@
       <c r="J7">
         <v>50</v>
       </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1.105899664099134</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8">
@@ -672,6 +684,12 @@
       </c>
       <c r="J8">
         <v>50</v>
+      </c>
+      <c r="K8">
+        <v>45</v>
+      </c>
+      <c r="L8">
+        <v>4.545732961314433</v>
       </c>
     </row>
     <row r="9">
@@ -743,6 +761,12 @@
       <c r="J10">
         <v>50</v>
       </c>
+      <c r="K10">
+        <v>45</v>
+      </c>
+      <c r="L10">
+        <v>2.881886426667809</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11">
@@ -813,6 +837,12 @@
       <c r="J12">
         <v>50</v>
       </c>
+      <c r="K12">
+        <v>45</v>
+      </c>
+      <c r="L12">
+        <v>0.4335377776643471</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
@@ -882,6 +912,12 @@
       </c>
       <c r="J14">
         <v>50</v>
+      </c>
+      <c r="K14">
+        <v>45</v>
+      </c>
+      <c r="L14">
+        <v>6.346135903644571</v>
       </c>
     </row>
     <row r="15">
@@ -915,6 +951,12 @@
       <c r="J15">
         <v>50</v>
       </c>
+      <c r="K15">
+        <v>45</v>
+      </c>
+      <c r="L15">
+        <v>4.440414510667493</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16">
@@ -946,6 +988,12 @@
       </c>
       <c r="J16">
         <v>50</v>
+      </c>
+      <c r="K16">
+        <v>45</v>
+      </c>
+      <c r="L16">
+        <v>3.428569895799778</v>
       </c>
     </row>
     <row r="17">

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -456,7 +456,7 @@
         <v>45</v>
       </c>
       <c r="L2">
-        <v>4.545732961314433</v>
+        <v>4.597378934590072</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -496,10 +496,10 @@
         <v>50</v>
       </c>
       <c r="K3">
-        <v>27.98</v>
+        <v>31.09</v>
       </c>
       <c r="L3">
-        <v>2.114001565380284</v>
+        <v>2.105302138243162</v>
       </c>
     </row>
     <row r="4">
@@ -689,7 +689,7 @@
         <v>45</v>
       </c>
       <c r="L8">
-        <v>4.545732961314433</v>
+        <v>4.597378934590072</v>
       </c>
     </row>
     <row r="9">
@@ -876,10 +876,10 @@
         <v>50</v>
       </c>
       <c r="K13">
-        <v>27.98</v>
+        <v>31.09</v>
       </c>
       <c r="L13">
-        <v>1.057000782690142</v>
+        <v>1.052651069121581</v>
       </c>
     </row>
     <row r="14">

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -1059,6 +1059,12 @@
       <c r="J18">
         <v>50</v>
       </c>
+      <c r="K18">
+        <v>30.93</v>
+      </c>
+      <c r="L18">
+        <v>2.048723542025793</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19">
@@ -1122,6 +1128,12 @@
       </c>
       <c r="J20">
         <v>50</v>
+      </c>
+      <c r="K20">
+        <v>45</v>
+      </c>
+      <c r="L20">
+        <v>4.596837270893258</v>
       </c>
     </row>
     <row r="21">
@@ -1187,6 +1199,12 @@
       <c r="J22">
         <v>50</v>
       </c>
+      <c r="K22">
+        <v>27.74</v>
+      </c>
+      <c r="L22">
+        <v>1.075237478181118</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23">
@@ -1218,6 +1236,12 @@
       </c>
       <c r="J23">
         <v>50</v>
+      </c>
+      <c r="K23">
+        <v>45</v>
+      </c>
+      <c r="L23">
+        <v>4.596837270893255</v>
       </c>
     </row>
     <row r="24">
@@ -1251,6 +1275,12 @@
       <c r="J24">
         <v>50</v>
       </c>
+      <c r="K24">
+        <v>11.22</v>
+      </c>
+      <c r="L24">
+        <v>2.176069808454578</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25">
@@ -1283,6 +1313,12 @@
       <c r="J25">
         <v>50</v>
       </c>
+      <c r="K25">
+        <v>45</v>
+      </c>
+      <c r="L25">
+        <v>2.880868705756837</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26">
@@ -1314,6 +1350,12 @@
       </c>
       <c r="J26">
         <v>50</v>
+      </c>
+      <c r="K26">
+        <v>45</v>
+      </c>
+      <c r="L26">
+        <v>-0.6438027686563839</v>
       </c>
     </row>
     <row r="27">
@@ -1379,6 +1421,12 @@
       <c r="J28">
         <v>50</v>
       </c>
+      <c r="K28">
+        <v>30.93</v>
+      </c>
+      <c r="L28">
+        <v>1.024361771012896</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29">
@@ -1410,6 +1458,12 @@
       </c>
       <c r="J29">
         <v>50</v>
+      </c>
+      <c r="K29">
+        <v>45</v>
+      </c>
+      <c r="L29">
+        <v>6.46353487298355</v>
       </c>
     </row>
     <row r="30">
@@ -1443,6 +1497,12 @@
       <c r="J30">
         <v>50</v>
       </c>
+      <c r="K30">
+        <v>4.77</v>
+      </c>
+      <c r="L30">
+        <v>2.265258684871176</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1475,6 +1535,12 @@
       <c r="J31">
         <v>50</v>
       </c>
+      <c r="K31">
+        <v>45</v>
+      </c>
+      <c r="L31">
+        <v>3.578477384090751</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32">
@@ -1506,6 +1572,12 @@
       </c>
       <c r="J32">
         <v>50</v>
+      </c>
+      <c r="K32">
+        <v>45</v>
+      </c>
+      <c r="L32">
+        <v>4.596837117020441</v>
       </c>
     </row>
     <row r="33">
@@ -1539,6 +1611,12 @@
       <c r="J33">
         <v>50</v>
       </c>
+      <c r="K33">
+        <v>30.94</v>
+      </c>
+      <c r="L33">
+        <v>2.048652774261071</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1570,6 +1648,12 @@
       </c>
       <c r="J34">
         <v>50</v>
+      </c>
+      <c r="K34">
+        <v>8.67</v>
+      </c>
+      <c r="L34">
+        <v>1.087410381677995</v>
       </c>
     </row>
     <row r="35">
@@ -1635,6 +1719,12 @@
       <c r="J36">
         <v>50</v>
       </c>
+      <c r="K36">
+        <v>43.14</v>
+      </c>
+      <c r="L36">
+        <v>1.393157580007649</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37">
@@ -1667,6 +1757,12 @@
       <c r="J37">
         <v>50</v>
       </c>
+      <c r="K37">
+        <v>9.59</v>
+      </c>
+      <c r="L37">
+        <v>1.044954826233629</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38">
@@ -1698,6 +1794,12 @@
       </c>
       <c r="J38">
         <v>50</v>
+      </c>
+      <c r="K38">
+        <v>45</v>
+      </c>
+      <c r="L38">
+        <v>4.596837117020441</v>
       </c>
     </row>
     <row r="39">
@@ -1730,6 +1832,12 @@
       </c>
       <c r="J39">
         <v>50</v>
+      </c>
+      <c r="K39">
+        <v>9.620000000000001</v>
+      </c>
+      <c r="L39">
+        <v>2.110482144870702</v>
       </c>
     </row>
     <row r="40">

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -1097,6 +1097,12 @@
       <c r="J19">
         <v>50</v>
       </c>
+      <c r="K19">
+        <v>4.77</v>
+      </c>
+      <c r="L19">
+        <v>1.132629342435588</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20">
@@ -1167,6 +1173,12 @@
       <c r="J21">
         <v>50</v>
       </c>
+      <c r="K21">
+        <v>43.14</v>
+      </c>
+      <c r="L21">
+        <v>1.393157560152119</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22">
@@ -1687,6 +1699,12 @@
       <c r="J35">
         <v>50</v>
       </c>
+      <c r="K35">
+        <v>45</v>
+      </c>
+      <c r="L35">
+        <v>4.596837117020441</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36">
@@ -1871,6 +1889,12 @@
       <c r="J40">
         <v>50</v>
       </c>
+      <c r="K40">
+        <v>8.030000000000001</v>
+      </c>
+      <c r="L40">
+        <v>1.510797020463879</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41">
@@ -1902,6 +1926,12 @@
       </c>
       <c r="J41">
         <v>50</v>
+      </c>
+      <c r="K41">
+        <v>45</v>
+      </c>
+      <c r="L41">
+        <v>-0.643802780018076</v>
       </c>
     </row>
     <row r="42">
@@ -1935,6 +1965,12 @@
       <c r="J42">
         <v>50</v>
       </c>
+      <c r="K42">
+        <v>45</v>
+      </c>
+      <c r="L42">
+        <v>0.4774344395161455</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43">
@@ -1967,6 +2003,12 @@
       <c r="J43">
         <v>50</v>
       </c>
+      <c r="K43">
+        <v>30.94</v>
+      </c>
+      <c r="L43">
+        <v>1.024326387130535</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44">
@@ -1998,6 +2040,12 @@
       </c>
       <c r="J44">
         <v>50</v>
+      </c>
+      <c r="K44">
+        <v>45</v>
+      </c>
+      <c r="L44">
+        <v>6.463534637251204</v>
       </c>
     </row>
     <row r="45">
@@ -2031,6 +2079,12 @@
       <c r="J45">
         <v>50</v>
       </c>
+      <c r="K45">
+        <v>8.67</v>
+      </c>
+      <c r="L45">
+        <v>2.17482076335599</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46">
@@ -2063,6 +2117,12 @@
       <c r="J46">
         <v>50</v>
       </c>
+      <c r="K46">
+        <v>7.95</v>
+      </c>
+      <c r="L46">
+        <v>3.548485763551627</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47">
@@ -2095,6 +2155,12 @@
       <c r="J47">
         <v>50</v>
       </c>
+      <c r="K47">
+        <v>45</v>
+      </c>
+      <c r="L47">
+        <v>4.597378934590072</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48">
@@ -2127,6 +2193,12 @@
       <c r="J48">
         <v>50</v>
       </c>
+      <c r="K48">
+        <v>45</v>
+      </c>
+      <c r="L48">
+        <v>4.597378934590072</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -2159,6 +2231,12 @@
       <c r="J49">
         <v>100</v>
       </c>
+      <c r="K49">
+        <v>45</v>
+      </c>
+      <c r="L49">
+        <v>5.161438489686421</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -2222,6 +2300,12 @@
       </c>
       <c r="J51">
         <v>500</v>
+      </c>
+      <c r="K51">
+        <v>45</v>
+      </c>
+      <c r="L51">
+        <v>21.80719244843208</v>
       </c>
     </row>
     <row r="52">

--- a/Figures/res.xlsx
+++ b/Figures/res.xlsx
@@ -1027,6 +1027,12 @@
       <c r="J17">
         <v>50</v>
       </c>
+      <c r="K17">
+        <v>45</v>
+      </c>
+      <c r="L17">
+        <v>4.596837270893258</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18">
@@ -1401,6 +1407,12 @@
       <c r="J27">
         <v>50</v>
       </c>
+      <c r="K27">
+        <v>45</v>
+      </c>
+      <c r="L27">
+        <v>0.4774347619553618</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28">
@@ -2268,6 +2280,12 @@
       </c>
       <c r="J50">
         <v>100</v>
+      </c>
+      <c r="K50">
+        <v>45</v>
+      </c>
+      <c r="L50">
+        <v>9.161438489686418</v>
       </c>
     </row>
     <row r="51">
